--- a/assets/constructions/examples/ctd_tsmb_radial_groove.xlsx
+++ b/assets/constructions/examples/ctd_tsmb_radial_groove.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK6"/>
+  <dimension ref="A1:AP6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,16 +614,41 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MGR8B1.5L22</t>
+          <t>M662GSW117L35RVBX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -631,35 +656,45 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PMKNSH</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>PMKNS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
       <c r="H2" t="n">
-        <v>8.1</v>
+        <v>6.2</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.96</v>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>5.96</v>
+      </c>
       <c r="O2" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="P2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -667,13 +702,15 @@
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>37.3</v>
+      </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>DER_DCON:8</t>
+          <t>VARGUS_D:6</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -681,10 +718,14 @@
           <t>WORKPIECE</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>VBX</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>TiCN</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -706,14 +747,33 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>DEREK Micro Boring. Инструмент для обработки отверстий малых диаметров.</t>
+          <t>2021/Groovex VARGUS</t>
+        </is>
+      </c>
+      <c r="AL2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>40.98</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AO2" t="n">
+        <v>3767.44</v>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R008M0200-30/AL41F</t>
+          <t>L004.0100-16/K10F</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -730,45 +790,47 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PMKNS</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>PKN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="H3" t="n">
-        <v>7.8</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="N3" t="n">
-        <v>7.3</v>
+        <v>3.5</v>
       </c>
       <c r="O3" t="n">
+        <v>16</v>
+      </c>
+      <c r="P3" t="n">
         <v>30</v>
       </c>
-      <c r="P3" t="n">
-        <v>50</v>
-      </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0.8</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -778,7 +840,7 @@
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>DUEM_DCON:8</t>
+          <t>DUEM_DCON:4</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -788,12 +850,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>AL41F</t>
+          <t>K10F</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -816,13 +878,32 @@
       <c r="AK3" t="inlineStr">
         <is>
           <t>Ultramini.pdf</t>
+        </is>
+      </c>
+      <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>48.81</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AO3" t="n">
+        <v>4487.28</v>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>PMKN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L006.0150-15/K10F</t>
+          <t>R005.0150-10/K10F</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -848,38 +929,38 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="M4" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="P4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="Q4" t="n">
         <v>1.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -889,7 +970,7 @@
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>DUEM_DCON:6</t>
+          <t>DUEM_DCON:5</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -927,94 +1008,87 @@
       <c r="AK4" t="inlineStr">
         <is>
           <t>Ultramini.pdf</t>
+        </is>
+      </c>
+      <c r="AL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>40.98</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AO4" t="n">
+        <v>3767.44</v>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>PMKN</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>105.0200.13163EG35</t>
+          <t>MGR8B1.5L22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HORN</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>HORN_105-6.4</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>HORN</t>
-        </is>
-      </c>
+          <t>DEREK</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
+          <t>PMKNSH</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>4.25</v>
+        <v>8.1</v>
       </c>
       <c r="I5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2.1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
-        <v>3.9</v>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="P5" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0.869</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>6.4</v>
-      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>HORN_B105.00..01</t>
+          <t>DER_DCON:8</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1022,14 +1096,10 @@
           <t>WORKPIECE</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>EG35</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>AlTiN</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1051,73 +1121,70 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Специнструмент</t>
+          <t>DEREK Micro Boring. Инструмент для обработки отверстий малых диаметров.</t>
+        </is>
+      </c>
+      <c r="AL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L006M0198-15/K10F</t>
+          <t>MGR8B2.0L30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DUEMMEL</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ULTRAMINI</t>
-        </is>
-      </c>
+          <t>DEREK</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PKN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
+          <t>PMKNSH</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>8.1</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5.3</v>
-      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="P6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1127,7 +1194,7 @@
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>DUEM_DCON:6</t>
+          <t>DER_DCON:8</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1135,14 +1202,10 @@
           <t>WORKPIECE</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>K10F</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>X</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -1164,7 +1227,18 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Ultramini.pdf</t>
+          <t>DEREK Micro Boring. Инструмент для обработки отверстий малых диаметров.</t>
+        </is>
+      </c>
+      <c r="AL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
